--- a/news_push_data/master/cna_master.xlsx
+++ b/news_push_data/master/cna_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,6 +2225,1869 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>川普威脅退出北約 共和黨大老麥康奈跨黨派聯手反對</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026/04/02 05:59</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-04-02T05:59:00+08:00</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020013.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>伊朗戰爭支持率狂瀉48百分點！傳統共和黨人轉向反戰</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026/04/02 05:44</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-04-02T05:44:00+08:00</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020012.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>伊朗總統致信美國民眾 溫情攻勢質疑川普師出無名</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026/04/02 04:17</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-04-02T04:17:00+08:00</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020009.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>美國男子臉書威脅殺害川普被捕 最重可吃40年牢飯</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026/04/02 03:36</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-04-02T03:36:00+08:00</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020008.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>伊朗報復美企第一槍？亞馬遜巴林雲端設施傳遇襲起火</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026/04/02 02:57</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-04-02T02:57:00+08:00</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020007.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>美媒：美伊正討論協議 以停火換取重啟荷莫茲海峽</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026/04/02 02:34</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-04-02T02:34:00+08:00</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020006.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>馬克宏會見高市早苗 互擺「龜派氣功」姿勢網路瘋傳</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026/04/02 01:30</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-04-02T01:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020005.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>范斯代川普下通牒：對伊朗失耐心 滿足美要求才停火</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026/04/02 01:21</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-04-02T01:21:00+08:00</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020004.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>川普出席最高法院言詞辯論 開在任總統歷史先例</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026/04/02 00:09</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-04-02T00:09:00+08:00</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020002.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>馬克宏在日本誇讚歐洲「可預測性」 暗批川普</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026/04/01 23:37</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-04-01T23:37:00+08:00</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010393.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>因應燃油成本上升 捷藍航空託運行李費最高漲9美元</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026/04/01 22:59</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-04-01T22:59:00+08:00</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010392.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>義大利三度無緣世足賽 體育部長砲轟應換足協主席</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026/04/01 22:33</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-04-01T22:33:00+08:00</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010389.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>歐盟援助烏克蘭 動用俄凍結資產利息520億元</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026/04/01 22:31</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-04-01T22:31:00+08:00</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010387.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>川普：美國很快會從伊朗戰事抽身 必要時將回頭打擊</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026/04/01 22:28</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-04-01T22:28:00+08:00</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010386.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>川普指伊朗總統尋求停火 德黑蘭稱荷莫茲不對敵人開放</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026/04/01 22:24</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-04-01T22:24:00+08:00</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010385.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>美伊戰火衝擊埃及外匯來源 風險與機會並存</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026/04/01 22:11</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-04-01T22:11:00+08:00</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604013002.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>英國本週召集約35國開會 討論如何重啟荷莫茲海峽</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026/04/01 21:56</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-04-01T21:56:00+08:00</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010381.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>法媒熱議高山離婚 學者稱荒野遺棄伴侶涉羞辱與支配</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026/04/01 21:22</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-04-01T21:22:00+08:00</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010376.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>美國獨立250週年 英王4/28赴美國會發表演說</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026/04/01 21:14</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-04-01T21:14:00+08:00</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010374.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>俄稱全面掌控烏東盧甘斯克州 基輔駁戰場半年來沒變化</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026/04/01 21:13</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-04-01T21:13:00+08:00</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010373.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>日法領袖就關鍵礦產供應鏈達協議 同意稀土採購合作</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026/04/01 20:14</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-04-01T20:14:00+08:00</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010357.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>美軍機飛越歌手搖滾小子家附近 戰爭部不懲處飛行員</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026/04/01 19:30</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-04-01T19:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010345.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>李在明主持經濟檢查會議 指示不要限購垃圾袋</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026/04/01 18:55</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-04-01T18:55:00+08:00</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010333.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>盟友拒挺對伊朗軍事行動 英媒：川普考慮退出北約</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026/04/01 18:12</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-04-01T18:12:00+08:00</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010316.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>日法領袖會談逢花季 高市與馬克宏開會前先賞櫻</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026/04/01 17:49</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-04-01T17:49:00+08:00</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010300.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>韓國因應能源危機 上調原油資源警報至「警戒」</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026/04/01 17:46</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-04-01T17:46:00+08:00</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010298.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>傳阿聯欲迫使荷莫茲海峽開放 恐成首個參戰波灣國家</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026/04/01 17:39</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-04-01T17:39:00+08:00</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010283.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>中東戰爭致區域情勢惡化 美國女記者在伊拉克遭綁架</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026/04/01 17:24</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-04-01T17:24:00+08:00</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010279.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>報復法國禁止運彈藥飛機通過領空 以色列將軍購降至零</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026/04/01 17:21</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-04-01T17:21:00+08:00</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010277.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>21位捷克主流媒體總編聯合聲明 籲總理尊重新聞業</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026/04/01 17:20</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-04-01T17:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010276.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>市場期待中東停戰 韓元兌美元回升、股市氛圍好轉</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026/04/01 17:18</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-04-01T17:18:00+08:00</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010273.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>日本JR最短幹線不敵虧損 成立115年後熄燈[影]</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026/04/01 16:58</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-04-01T16:58:00+08:00</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010264.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>4月1日 美伊戰爭對國際經濟、財經市場與民生衝擊</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026/04/01 16:40</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-04-01T16:40:00+08:00</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010252.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>波蘭實施油價上限 捷克人開車前往邊境加油</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026/04/01 16:39</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-04-01T16:39:00+08:00</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010250.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>日媒：日本考慮導入攻擊型無人機搭配長程飛彈</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026/04/01 15:54</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-04-01T15:54:00+08:00</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010218.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>電子入境卡擬刪出發地、目的地欄位 韓外交部：非政治性問題</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026/04/01 15:38</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-04-01T15:38:00+08:00</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010209.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>無人機偏航擾波羅的海國家 芬蘭參考烏克蘭強化預警</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026/04/01 15:12</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-04-01T15:12:00+08:00</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010198.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>中東局勢衝擊能源 亞洲多國以物易物解燃眉之急</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026/04/01 14:18</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-04-01T14:18:00+08:00</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010173.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>油價飆漲 立陶宛推火車票價減半降低民眾負擔</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026/04/01 14:01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-04-01T14:01:00+08:00</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010162.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>荷蘭慶同婚25週年 總理葉騰計劃近期步入禮堂</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026/04/01 13:57</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-04-01T13:57:00+08:00</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010161.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>兒少禁令未落實 澳洲考慮控告FB、TikTok等社群平台</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026/04/01 13:55</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-04-01T13:55:00+08:00</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010160.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>阿聯禁伊朗籍人士入境、轉機 波灣緊張局勢升溫</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026/04/01 13:35</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-04-01T13:35:00+08:00</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010143.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>教宗籲川普尋求停戰 盼復活節前結束中東衝突</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026/04/01 13:33</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-04-01T13:33:00+08:00</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010142.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>伊朗無人機襲科威特 機場油槽起火損害嚴重</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026/04/01 13:29</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-04-01T13:29:00+08:00</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010141.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>韓國掀垃圾袋搶購潮 政府考慮設限購制</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026/04/01 13:27</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-04-01T13:27:00+08:00</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010140.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>阿根廷將伊朗革命衛隊列為恐怖組織 與美國立場一致</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026/04/01 12:45</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-04-01T12:45:00+08:00</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010130.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>日法領袖會談在即 雙方將同意共同採購稀土</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026/04/01 12:34</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-04-01T12:34:00+08:00</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010122.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>美期中選舉前 川普簽行政命令收緊郵寄投票法規</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026/04/01 12:17</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-04-01T12:17:00+08:00</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010115.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>白宮：川普4/2將就伊朗戰事發表全國演說</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026/04/01 12:03</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-04-01T12:03:00+08:00</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010106.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>海地幫派猖獗 地方火力不足自衛無效</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026/04/01 12:01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-04-01T12:01:00+08:00</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010105.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>中東戰爭第32天》美擬2、3週內結束伊朗戰事 最新發展一次看</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026/04/01 11:39</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-04-01T11:39:00+08:00</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010091.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>日航與全日空將漲燃油附加費 飛台灣漲幅逾50%</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026/04/01 11:32</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-04-01T11:32:00+08:00</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010078.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>盧比歐：伊朗戰爭終點在望 美戰後將審視與北約關係</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026/04/01 11:30</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-04-01T11:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010076.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>美法官下令停建白宮大宴會廳 川普政府火速提上訴</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026/04/01 11:17</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-04-01T11:17:00+08:00</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010074.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>甲骨文出手裁數千人 加碼AI對抗雲端強敵</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026/04/01 10:46</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-04-01T10:46:00+08:00</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010061.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>因應燃料危機 澳洲2州祭大眾運輸免費優惠</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026/04/01 10:37</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-04-01T10:37:00+08:00</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010056.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>油價飆漲 民調：約66%美國人盼儘快結束伊朗戰爭</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026/04/01 10:25</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-04-01T10:25:00+08:00</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010050.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>聯合國：中東戰爭恐吞噬阿拉伯國家2025年經濟成長</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026/04/01 09:50</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-04-01T09:50:00+08:00</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010042.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>日本茨城縣發生規模5.0地震 未引發海嘯</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026/04/01 09:42</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-04-01T09:42:00+08:00</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010039.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>開普敦幫派衝突11天83死 800名士兵將部署當地</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026/04/01 08:56</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-04-01T08:56:00+08:00</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010028.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>微軟攜手雪佛龍及Engine No. 1 簽訂供電協議</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026/04/01 08:46</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-04-01T08:46:00+08:00</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010027.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>川普：無論有無協議 美國將在2、3週內撤離伊朗</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026/04/01 08:44</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-04-01T08:44:00+08:00</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010026.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>美人道放行 俄油輪到港73萬桶原油暫解古巴危機</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026/04/01 08:35</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-04-01T08:35:00+08:00</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010023.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>馬斯克批加拿大虛偽不公平 再度惹惱加拿大人</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026/04/01 08:33</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-04-01T08:33:00+08:00</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010022.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>美參議員將提案擴大中國車禁令 籲其他國家跟進</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026/04/01 08:31</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-04-01T08:31:00+08:00</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010021.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>俄軍用運輸機撞山壁墜毀29死 初判技術故障所致</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026/04/01 08:26</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-04-01T08:26:00+08:00</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010020.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>義大利電影城公布亮眼財報 將製作刺客教條等大片</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026/04/01 07:43</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-04-01T07:43:00+08:00</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010017.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>中東局勢難解 高油價燒向美國</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026/04/01 07:25</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-04-01T07:25:00+08:00</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010016.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>川普挑戰出生公民權憲法修正案 最高法院見真章</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026/04/01 07:22</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-04-01T07:22:00+08:00</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604010015.aspx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/master/cna_master.xlsx
+++ b/news_push_data/master/cna_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4088,6 +4088,1869 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>川普祭新藥品關稅、重整金屬稅 強推製造業回流美國</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026/04/03 04:49</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-04-03T04:49:00+08:00</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030007.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>英召集約40國談荷莫茲危機 要求立即無條件重開海峽</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026/04/03 03:34</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-04-03T03:34:00+08:00</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030005.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>不滿艾普斯坦案處置方式 川普撤換美司法部長邦迪</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026/04/03 02:37</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-04-03T02:37:00+08:00</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030004.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>伊朗擬對通過荷莫茲海峽船舶收費 與阿曼起草通行協議</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026/04/03 02:20</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-04-03T02:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604033001.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>美支持巴拿馬抗中扣押船舶 盧比歐批北京損害法治</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026/04/03 01:04</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-04-03T01:04:00+08:00</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030003.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>遭到美、以數波攻擊 伊朗兩大鋼鐵廠被迫停擺</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026/04/02 21:55</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-04-02T21:55:00+08:00</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020362.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>美國關稅衝擊 比利時科技業損失1500個工作機會</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026/04/02 21:31</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-04-02T21:31:00+08:00</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020358.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>烏干達幼兒園爆持刀攻擊案 4幼童身亡</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026/04/02 21:13</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-04-02T21:13:00+08:00</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020353.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>捷克油價攀升 政府將限制燃油業者利潤</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026/04/02 20:25</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-04-02T20:25:00+08:00</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020340.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>能源危機加劇 孟加拉桶裝瓦斯漲價29%</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026/04/02 20:22</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-04-02T20:22:00+08:00</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020338.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>中東衝突未歇 伊朗再否認重啟鈾濃縮製造核武</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026/04/02 20:14</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-04-02T20:14:00+08:00</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020335.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>馬克宏稱武力解放荷莫茲海峽「不切實際」</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026/04/02 20:14</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-04-02T20:14:00+08:00</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020334.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>泰國大麻店3年內須轉型成診所 全面僅限醫療用</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026/04/02 20:12</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-04-02T20:12:00+08:00</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020330.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>烏克蘭無人機3度墜芬蘭 第3架距俄邊境僅1公里</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026/04/02 19:33</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-04-02T19:33:00+08:00</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020319.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>伊朗秘密網絡重建自殺無人機部隊 美情報揭中、港公司供零件</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026/04/02 19:24</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-04-02T19:24:00+08:00</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020313.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>KitKat架追蹤器盼尋回失竊商品 官方聲明：不是愚人節玩笑</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026/04/02 19:14</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-04-02T19:14:00+08:00</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604025002.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>外長通話 伊朗承諾菲律賓籍油輪安全通行</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026/04/02 19:00</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-04-02T19:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020302.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>荷莫茲海峽遭封鎖 越南：支持航行自由與安全</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026/04/02 18:31</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-04-02T18:31:00+08:00</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020287.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>緬甸國會4/3選新總統 軍政府領袖是3名人選之一</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026/04/02 18:23</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-04-02T18:23:00+08:00</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020284.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>法極右翼市長撤歐盟旗幟掀議論 黨內對歐立場現分歧</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026/04/02 18:07</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-04-02T18:07:00+08:00</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020281.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>中東戰爭衝擊 不丹調漲燃油價格</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026/04/02 17:56</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-04-02T17:56:00+08:00</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020277.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>中東局勢推升能源價格 日相不排除要求節電</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026/04/02 17:47</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-04-02T17:47:00+08:00</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020271.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>從衝浪到賽狗都能賭 澳洲加強管制博弈廣告</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026/04/02 16:57</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-04-02T16:57:00+08:00</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020238.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>川普演說宣告對伊朗戰果 實力嚇阻與戰略矛盾並存</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026/04/02 16:41</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-04-02T16:41:00+08:00</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020233.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>日本濱壽司食物中毒39人不適 驗出諾羅病毒</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026/04/02 16:39</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-04-02T16:39:00+08:00</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020230.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>美駐巴格達大使館警告 親伊朗團體2天內恐發動攻擊</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026/04/02 16:36</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-04-02T16:36:00+08:00</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020228.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>4月2日 美伊戰爭對國際經濟、財經市場與民生衝擊</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026/04/02 16:30</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-04-02T16:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020226.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>中東衝突影響 印度航空公司調升燃油費、機票漲價</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026/04/02 16:28</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-04-02T16:28:00+08:00</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020225.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>馬克宏訪日充滿漫畫元素 與高市擺「發功」姿勢[影]</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026/04/02 15:50</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-04-02T15:50:00+08:00</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020207.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>李在明國會演說 盼盡快通過中東危機追加預算案</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026/04/02 15:45</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-04-02T15:45:00+08:00</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020205.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>協助死亡組織能否進入醫院安養院 瑞士掀辯論</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026/04/02 15:34</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-04-02T15:34:00+08:00</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020199.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>川普揚言將伊打回石器時代 德黑蘭威脅毀滅性攻擊美以</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026/04/02 15:15</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-04-02T15:15:00+08:00</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020190.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>甲骨文傳裁員3萬人 印度1.2萬人失業衝擊最大</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026/04/02 14:28</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-04-02T14:28:00+08:00</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020166.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>川普誓言加強對伊朗打擊 油價飆漲全球股市下挫</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026/04/02 14:23</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-04-02T14:23:00+08:00</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020162.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>美媒：FBI認定中國駭客入侵系統 構成重大國安威脅</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026/04/02 14:18</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-04-02T14:18:00+08:00</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020159.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>金融時報：美擬對藥品徵100%關稅 促製藥業回流</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026/04/02 14:02</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-04-02T14:02:00+08:00</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020154.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>紐西蘭內閣改組 前海軍軍官潘克出任國防部長</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026/04/02 13:41</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-04-02T13:41:00+08:00</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020143.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>林佳龍：台美共生夥伴關係 共推更安全可信賴供應鏈</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026/04/02 13:34</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-04-02T13:34:00+08:00</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020138.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Axios評伊朗戰爭：軍事達標、戰略落空、政經失血</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026/04/02 13:05</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-04-02T13:05:00+08:00</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020133.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>菲律賓強烈譴責中國海上挑釁 強調採外交途徑交涉</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026/04/02 12:45</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-04-02T12:45:00+08:00</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020124.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>中東危機美歐生裂痕 川普能否讓美國退出北約分析一次看</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026/04/02 12:41</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-04-02T12:41:00+08:00</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020122.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>無視川普演說 以軍：攔截伊朗3波飛彈攻擊</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026/04/02 12:40</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-04-02T12:40:00+08:00</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020121.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>川普闡述伊朗戰爭理由 細節未明惹質疑</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026/04/02 12:39</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-04-02T12:39:00+08:00</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020119.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>漲價仍不敷成本 日航與全日空考慮修改燃油附加費制度</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026/04/02 12:36</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-04-02T12:36:00+08:00</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020117.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>中東戰爭第33天》川普稱戰事接近尾聲 最新發展一次看</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026/04/02 12:01</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-04-02T12:01:00+08:00</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020106.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>川普稱伊朗戰事近結束 紐時：5大目標只達成1項</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026/04/02 11:50</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-04-02T11:50:00+08:00</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020099.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>日法領袖會談聲明 確認台海和平穩定重要性</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026/04/02 11:36</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-04-02T11:36:00+08:00</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020080.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>韓垃圾袋限購制被青瓦台否決 氣候部：不限制購買</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026/04/02 11:24</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-04-02T11:24:00+08:00</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020076.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>美貿易報告揭美豬、農產障礙 緊盯台灣ART承諾</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026/04/02 11:11</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-04-02T11:11:00+08:00</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020068.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>川普演說重申舊立場 專家：美國民眾疑惑加深</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026/04/02 11:11</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-04-02T11:11:00+08:00</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020067.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>川普批歐洲盟友「紙老虎」 北約秘書長下週訪美</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026/04/02 10:51</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-04-02T10:51:00+08:00</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020062.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>印尼近海強震海嘯警報解除 餘震規模5.5</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026/04/02 10:45</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-04-02T10:45:00+08:00</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020058.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>美解除制裁委內瑞拉臨時總統 石油資產動向受注目</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026/04/02 10:31</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-04-02T10:31:00+08:00</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020053.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>捷克國家博物館3D建模技術 助烏克蘭保存瀕危古蹟</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026/04/02 10:24</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-04-02T10:24:00+08:00</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020051.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>因應中國與台海風險 日本強化西南離島防衛布局</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026/04/02 10:21</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-04-02T10:21:00+08:00</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020048.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>川普稱戰事已近結束 兩三週內將伊朗打回石器時代</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026/04/02 10:19</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-04-02T10:19:00+08:00</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020046.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>川普：對伊開戰為必要之舉 以回應近半世紀暴力</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026/04/02 10:11</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-04-02T10:11:00+08:00</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020043.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>印尼近海規模7.4強震 小海嘯波可能影響台灣</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026/04/02 10:03</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-04-02T10:03:00+08:00</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020041.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>川普威脅斷烏克蘭軍援 逼歐洲聯手護航荷莫茲海峽</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026/04/02 09:51</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-04-02T09:51:00+08:00</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020040.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>印尼外海強震 北蘇拉威西省建物倒塌已釀1死1傷</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026/04/02 09:44</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-04-02T09:44:00+08:00</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020037.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>川普：未來2到3週將給伊朗最重擊 未達成協議將打擊供電網[影]</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026/04/02 09:29</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-04-02T09:29:00+08:00</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604023002.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>川普全國演說：對伊朗戰爭取得壓倒性勝利[影]</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026/04/02 09:17</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-04-02T09:17:00+08:00</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604023001.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>庫克群島與紐西蘭新簽防務協議 緩解緊張關係</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026/04/02 08:38</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-04-02T08:38:00+08:00</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020023.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>美伊衝突加劇 巴西推動柴油自給計畫</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026/04/02 08:24</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-04-02T08:24:00+08:00</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020022.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>川普將發表全國演說 擬宣布對伊戰爭目標達成[影]</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026/04/02 07:53</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-04-02T07:53:00+08:00</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020019.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>愚人節藝術建國 立陶宛「對岸共和國」歡慶28週年</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026/04/02 07:53</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-04-02T07:53:00+08:00</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020018.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>美出生公民權最高法院開庭 「黃金德案」後代旁聽</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026/04/02 07:45</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-04-02T07:45:00+08:00</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020017.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>印尼東部外海規模7.4強震 引發海嘯警報</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026/04/02 07:41</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-04-02T07:41:00+08:00</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020016.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>捷克計劃2030年發射首顆國產衛星 強化太空自主性</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026/04/02 07:24</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-04-02T07:24:00+08:00</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604020015.aspx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/master/cna_master.xlsx
+++ b/news_push_data/master/cna_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E205"/>
+  <dimension ref="A1:E268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5951,6 +5951,1707 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>傳美軍A-10墜毀飛行員獲救 伊朗擊落F-15一獲救一失聯</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026/04/04 05:45</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-04-04T05:45:00+08:00</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040006.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>以色列空襲貝魯特 美警告伊朗恐攻擊黎巴嫩大學院校</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026/04/04 04:04</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-04-04T04:04:00+08:00</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040005.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>川普接獲美軍戰機被擊落簡報 搜尋失聯人員仍在進行</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026/04/04 02:47</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-04-04T02:47:00+08:00</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040003.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>傳美F-15E雙座戰機遭伊朗擊落 其中一名機員獲救</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026/04/04 01:25</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-04-04T01:25:00+08:00</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040002.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>美國3月大增17.8萬名就業人口 失業率略降至4.3%</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026/04/03 23:23</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-04-03T23:23:00+08:00</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030246.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>廣島原爆資料館2025年度258萬人次入館 再寫下新高</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2026/04/03 22:47</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-04-03T22:47:00+08:00</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030244.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>伊朗頻道稱美戰機飛行員彈射逃生 中央司令部未證實</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2026/04/03 22:18</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-04-03T22:18:00+08:00</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030241.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>以色列稱已摧毀伊朗70%鋼鐵產能 重創武器製造能力</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2026/04/03 22:14</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-04-03T22:14:00+08:00</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030240.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>伊朗戰爭持續 白宮提議2027年國防預算1.5兆美元</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2026/04/03 22:04</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-04-03T22:04:00+08:00</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030237.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>與以色列、烏克蘭總統通話 教宗良十四世呼籲和平</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2026/04/03 21:20</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-04-03T21:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030231.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>阿布達比防空系統攔截攻擊 碎片墜落造成至少12傷</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2026/04/03 21:15</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-04-03T21:15:00+08:00</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030230.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>柬埔寨國會通過首部打詐法 詐騙中心猖獗引國際壓力</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2026/04/03 20:38</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-04-03T20:38:00+08:00</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030225.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>3月聯合國糧價指數漲2.4% 穀物供應足緩和植物油漲價衝擊</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026/04/03 20:12</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-04-03T20:12:00+08:00</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030222.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>澤倫斯基：前線守住 烏克蘭近10個月最佳形勢</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2026/04/03 20:10</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-04-03T20:10:00+08:00</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030221.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>俄軍一架蘇-30戰機墜毀克里米亞 失事原因不明</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2026/04/03 20:04</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-04-03T20:04:00+08:00</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030220.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>伊朗醫療設施遭空襲 世衛示警：多處公衛體系受創</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2026/04/03 19:59</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026-04-03T19:59:00+08:00</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030218.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>確保荷莫茲海峽通行安全 比利時願協助掃雷</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2026/04/03 19:11</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026-04-03T19:11:00+08:00</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030210.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>台人居留證錯登中國 丹麥友台組織：剝奪台灣人認同</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2026/04/03 18:50</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-04-03T18:50:00+08:00</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030205.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>科威特海水淡化廠又遭伊朗攻擊 官員稱受實質損壞</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2026/04/03 18:40</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-04-03T18:40:00+08:00</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030202.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>馬克宏聲望短暫回升又跌 近8成法國人憂黃背心再現</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2026/04/03 18:37</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2026-04-03T18:37:00+08:00</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030201.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>紐澳受燃料短缺衝擊 復活節出遊計畫打亂電動車大賣</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2026/04/03 18:19</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2026-04-03T18:19:00+08:00</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030194.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>日本公開閣員資產 防衛大臣小泉進次郎居首</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2026/04/03 18:09</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026-04-03T18:09:00+08:00</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030188.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>俄24小時連番空襲烏前線 射10枚飛彈400多架無人機</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2026/04/03 17:50</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026-04-03T17:50:00+08:00</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030182.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>伊朗地面戰一觸即發 美陸軍最高首長突遭撤換</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2026/04/03 17:44</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026-04-03T17:44:00+08:00</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030178.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>為解決尖峰時刻人潮 韓國擬推公部門彈性上下班</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2026/04/03 17:35</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026-04-03T17:35:00+08:00</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030165.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>美戰爭部長宣布 將准軍人攜私人武器進入軍事基地</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2026/04/03 17:34</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026-04-03T17:34:00+08:00</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030164.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>油價上漲 星國私人包機業者：適度調整價格反映成本</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2026/04/03 17:27</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2026-04-03T17:27:00+08:00</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030162.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>墨西哥中部小型飛機墜毀 導致4人喪命</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2026/04/03 17:15</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026-04-03T17:15:00+08:00</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030159.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>印度展開人口普查 近百年首度全面登錄種姓</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2026/04/03 17:09</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026-04-03T17:09:00+08:00</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030157.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>以色列：對黎巴嫩攻勢一個月來打擊逾3500個目標</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2026/04/03 16:50</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026-04-03T16:50:00+08:00</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030152.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>俄羅斯列車出軌至少22傷 當局展開調查</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2026/04/03 16:35</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026-04-03T16:35:00+08:00</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030150.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>4月3日 美伊戰爭對國際經濟、財經市場與民生衝擊</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2026/04/03 16:31</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026-04-03T16:31:00+08:00</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030148.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>傳日本政府擬率商界訪俄 政府發言人否認</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2026/04/03 16:28</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2026-04-03T16:28:00+08:00</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030146.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>韓國導演金昌民遭圍毆身亡 引社會公憤批調查不力</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2026/04/03 16:21</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-04-03T16:21:00+08:00</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030144.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>汽車大廠斯特蘭蒂斯 加拿大組裝中國電動車遭拒絕</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2026/04/03 16:13</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026-04-03T16:13:00+08:00</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030142.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>安理會延後表決護航荷莫茲海峽提案 伊朗警告勿挑釁</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2026/04/03 15:56</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026-04-03T15:56:00+08:00</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030135.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>美伊戰爭衝擊芬蘭人荷包 油箱到菜籃無一倖免</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2026/04/03 15:44</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026-04-03T15:44:00+08:00</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030131.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>緬甸軍政府領袖敏昂萊當選總統 以文人身分延續統治</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2026/04/03 15:38</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026-04-03T15:38:00+08:00</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030128.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>伊朗處決18歲抗議少年 人權組織批速審極度不公</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2026/04/03 14:50</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026-04-03T14:50:00+08:00</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030119.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>沙烏地基地美軍E3預警機遭毀 多架軍機露天停放</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2026/04/03 14:48</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026-04-03T14:48:00+08:00</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030118.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>前統一教會欲捲土重來 擬設新團體接收捐款</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2026/04/03 14:28</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026-04-03T14:28:00+08:00</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030112.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>德國列車驚傳持刀男施放煙火12傷 乘客反鎖制伏嫌犯</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2026/04/03 14:07</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026-04-03T14:07:00+08:00</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030108.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>馬克宏李在明會談 合作確保荷莫茲海峽安全通道</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2026/04/03 13:47</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2026-04-03T13:47:00+08:00</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030101.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>美國補齊戰斧飛彈庫需5年 分析：削弱台海嚇阻力</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2026/04/03 13:37</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-04-03T13:37:00+08:00</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604033004.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>金正恩視察平壤新住宅區 偕女兒逛寵物店摸貓狗</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2026/04/03 13:20</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2026-04-03T13:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030090.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>美國會提案聯手盟友 強化晶片設備出口中國管制</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2026/04/03 13:17</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026-04-03T13:17:00+08:00</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604033003.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>CNN：美情報估伊朗仍保有大量飛彈發射能力</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2026/04/03 13:03</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2026-04-03T13:03:00+08:00</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030087.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>菲律賓聖週進入高潮 小馬可仕籲以謙卑與慈悲生活</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2026/04/03 13:02</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2026-04-03T13:02:00+08:00</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030086.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>日媒：日本擬率商界訪俄 可能談及採購原油</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2026/04/03 12:16</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2026-04-03T12:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030079.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>川普：美尚未開始摧毀伊朗剩餘目標 鎖定橋梁電廠</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2026/04/03 12:05</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2026-04-03T12:05:00+08:00</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030075.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>上任不到一年 德國總理梅爾茨政府滿意度剩15%</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2026/04/03 11:56</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2026-04-03T11:56:00+08:00</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030072.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>中東戰爭第34天》川普稱伊朗最高橋梁被毀 最新發展一次看</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2026/04/03 11:51</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2026-04-03T11:51:00+08:00</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030070.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>傳川普考慮再換閣員 美媒點名商務部長勞工部長</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2026/04/03 11:13</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026-04-03T11:13:00+08:00</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030047.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>逾百名國際法學者公開信 憂美軍行動恐涉戰爭罪</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2026/04/03 11:08</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2026-04-03T11:08:00+08:00</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030045.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>白宮宴會廳興建過關卻卡關 法院裁定須先經國會同意</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2026/04/03 10:57</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2026-04-03T10:57:00+08:00</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030043.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>對等關稅重塑全球貿易版圖 台灣對美出口飆升逾8成超越日韓</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2026/04/03 09:21</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2026-04-03T09:21:00+08:00</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030027.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>川普對等關稅一年 簽逾20項協議、政策修改逾50次</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2026/04/03 09:01</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2026-04-03T09:01:00+08:00</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030022.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>川普與伊朗互放狠話 全球急盼荷莫茲海峽重啟</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2026/04/03 08:50</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2026-04-03T08:50:00+08:00</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030020.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>澤倫斯基願傳授黑海經驗 協助中東重啟荷莫茲海峽</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>2026/04/03 08:07</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-04-03T08:07:00+08:00</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030015.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>禁用星鏈終端和烏軍反攻見效 俄軍前線推進明顯降溫</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2026/04/03 07:29</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-04-03T07:29:00+08:00</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030012.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>川普稱伊朗最高橋樑被毀 警告快談判終戰</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2026/04/03 07:00</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-04-03T07:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030011.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>傳遭赫格塞斯要求卸職 美陸軍參謀長將提前退休</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2026/04/03 06:03</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026-04-03T06:03:00+08:00</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030010.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>伊朗稱攻擊中東3國美以目標 葉門叛軍再朝以色列射彈</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2026/04/03 06:01</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-04-03T06:01:00+08:00</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604030009.aspx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/master/cna_master.xlsx
+++ b/news_push_data/master/cna_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E268"/>
+  <dimension ref="A1:E308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7652,6 +7652,1086 @@
         </is>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>艾爾段會晤澤倫斯基 商討能源航運安全與終結戰爭</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2026/04/05 05:44</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2026-04-05T05:44:00+08:00</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050007.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>以色列襲伊朗石化廠 尼坦雅胡：持續打擊德黑蘭政權</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2026/04/05 04:37</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2026-04-05T04:37:00+08:00</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050005.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>已故伊朗將領蘇雷曼尼親屬美國被捕 綠卡遭撤銷</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2026/04/05 01:36</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2026-04-05T01:36:00+08:00</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050003.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>俄企自伊朗布什爾核電廠再撤198人 1員工死於彈片</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2026/04/04 23:10</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2026-04-04T23:10:00+08:00</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040217.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>川普下達48小時通牒 伊朗若不讓步「地獄將降臨」</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2026/04/04 22:59</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2026-04-04T22:59:00+08:00</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040216.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>伊朗持續搜捕美軍失聯飛官 稱仍對和談持開放態度</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2026/04/04 21:38</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2026-04-04T21:38:00+08:00</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040213.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>阿富汗5.8強震增至12死4傷 含1家8人罹難</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2026/04/04 21:38</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2026-04-04T21:38:00+08:00</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040212.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>澤倫斯基抵達土耳其 將與艾爾段商討安全議題</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2026/04/04 21:04</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2026-04-04T21:04:00+08:00</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040209.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>中東戰爭進入35天 美國已損失7架載人軍機</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2026/04/04 19:57</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2026-04-04T19:57:00+08:00</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040201.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>伊朗多地遇襲 美以轟核電廠、水泥廠與石化中心</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2026/04/04 19:43</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2026-04-04T19:43:00+08:00</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040199.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>在法台商展示高端工具機 應用廣泛未受油價波動影響</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2026/04/04 19:31</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2026-04-04T19:31:00+08:00</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040196.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>俄羅斯無人機攻擊烏克蘭東部市場 導致5死19傷</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2026/04/04 19:23</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2026-04-04T19:23:00+08:00</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040195.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>TIME：白宮幕僚長憂美化戰報誤導川普 籲直言不諱</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2026/04/04 18:41</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2026-04-04T18:41:00+08:00</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040188.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>紐時標題寫錯NATO全名挨批 北約變北美公約組織</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>2026/04/04 18:17</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2026-04-04T18:17:00+08:00</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040183.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>伊朗大橋被炸 中國警告在以公民遠離重要設施</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2026/04/04 17:53</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2026-04-04T17:53:00+08:00</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040174.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>美國加徵汽車關稅滿1年 日本車廠迎「新常態」</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2026/04/04 17:39</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2026-04-04T17:39:00+08:00</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040167.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>中東戰火延燒5週 美戰爭部：13官兵亡、365人傷</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2026/04/04 17:35</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2026-04-04T17:35:00+08:00</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040165.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>4月4日 美伊戰爭對國際經濟、財經市場與民生衝擊</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2026/04/04 16:28</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2026-04-04T16:28:00+08:00</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040140.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>減少石油消耗 越南E10生物汽油提前全國上路</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>2026/04/04 16:19</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2026-04-04T16:19:00+08:00</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040138.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>美擴大打擊中國科技產品 FCC擬禁部分設備進口</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>2026/04/04 15:33</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2026-04-04T15:33:00+08:00</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040120.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>川普簽令強化大學體育規範 籲國會盡速立法</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2026/04/04 14:58</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2026-04-04T14:58:00+08:00</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040118.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>伊朗襲美駐沙烏地阿拉伯使館 華爾街日報：損害比先前披露嚴重</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>2026/04/04 14:37</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2026-04-04T14:37:00+08:00</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040116.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>彭博：伊朗戰事戰斧飛彈耗費鉅 恐影響交貨日本</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2026/04/04 14:05</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2026-04-04T14:05:00+08:00</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604043001.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>美軍F-15墜伊朗如何尋人？戰鬥搜救進行方式一次看懂</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2026/04/04 13:49</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2026-04-04T13:49:00+08:00</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040107.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>燃料價格飆漲 定置網漁法成菲漁民生計替代方案</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2026/04/04 13:48</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2026-04-04T13:48:00+08:00</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040106.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>華郵：美以不解殉道文化 斬首反促伊朗堅定抵抗</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2026/04/04 13:44</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2026-04-04T13:44:00+08:00</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040105.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>美伊開戰後 首艘日本相關船隻通過荷莫茲海峽</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2026/04/04 12:16</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2026-04-04T12:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040075.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>荷莫茲海峽成籌碼 美情報稱伊朗短期難解封</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2026/04/04 12:15</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2026-04-04T12:15:00+08:00</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040074.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>分析：美軍機1天內接連折翼 伊朗戰力保存策略奏效</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2026/04/04 12:11</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2026-04-04T12:11:00+08:00</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040071.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>中東戰爭第35天》美戰機遭擊落、川普增軍費 最新發展一次看</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2026/04/04 11:51</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2026-04-04T11:51:00+08:00</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040066.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>白宮提1.5億美元預算重啟惡魔島 裴洛西矢言阻擋</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>2026/04/04 11:36</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2026-04-04T11:36:00+08:00</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040061.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>美國土安全部局部停擺 川普簽令補發薪資</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2026/04/04 11:09</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>2026-04-04T11:09:00+08:00</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040045.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>東京澀谷知名交叉路口 男子在路上縱火被捕[影]</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2026/04/04 10:41</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2026-04-04T10:41:00+08:00</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040039.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>法國貨輪通過荷莫茲海峽 戰爭以來首艘西歐船舶</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>2026/04/04 10:26</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2026-04-04T10:26:00+08:00</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040038.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>美戰機遭擊落 川普回應不影響與伊朗談判</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2026/04/04 10:03</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-04-04T10:03:00+08:00</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040033.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>美2戰機遭擊落搜救機遇襲 伊朗攻擊鄰國擴大戰事[影]</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2026/04/04 09:16</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2026-04-04T09:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040021.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>安理會延後表決荷莫茲海峽決議 中國反對授權動武</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2026/04/04 08:45</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2026-04-04T08:45:00+08:00</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040015.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>蘇黎世復活節新傳統 玫瑰噴泉接住現代人脆弱</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>2026/04/04 07:57</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2026-04-04T07:57:00+08:00</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040011.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>義總理無預警出訪中東3國 盼緩解能源危機</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>2026/04/04 07:30</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026-04-04T07:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040009.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>阿富汗發生規模5.9強震 已知8死1傷</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>2026/04/04 06:23</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2026-04-04T06:23:00+08:00</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604040008.aspx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/master/cna_master.xlsx
+++ b/news_push_data/master/cna_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E308"/>
+  <dimension ref="A1:E345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8732,6 +8732,1005 @@
         </is>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>德州油罐車撞電線起火 司機燒傷情況危急</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>2026/04/06 05:51</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2026-04-06T05:51:00+08:00</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604060008.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>遭烏攻擊中斷運作 傳俄波羅的海港口恢復原油裝載</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>2026/04/06 05:22</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026-04-06T05:22:00+08:00</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604060007.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>油輪載伊拉克原油通過荷莫茲海峽 將在馬來西亞卸貨</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>2026/04/06 04:45</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-04-06T04:45:00+08:00</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604060006.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>教宗良十四世首份復活節文告 敦促權勢者選擇和平</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>2026/04/06 03:42</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2026-04-06T03:42:00+08:00</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604060005.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>OPEC+：受損能源設施修復費時且昂貴</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>2026/04/06 02:52</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2026-04-06T02:52:00+08:00</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604060004.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>開放荷莫茲海峽最後通牒 川普暗示美東4/7晚間8時</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>2026/04/06 02:24</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2026-04-06T02:24:00+08:00</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604060003.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>伊朗持續空襲鄰國 阿聯：準備好加入美國為首行動</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>2026/04/06 00:45</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2026-04-06T00:45:00+08:00</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604060002.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>福斯新聞：川普稱4/6有機會與伊朗達成協議</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2026/04/05 22:52</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2026-04-05T22:52:00+08:00</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050194.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>美軍成功營救F-15E飛官 川普將召開記者會說明</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>2026/04/05 22:40</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2026-04-05T22:40:00+08:00</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050193.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>川普重申開放海峽 揚言4/7打擊伊朗發電廠與橋梁</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>2026/04/05 22:09</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2026-04-05T22:09:00+08:00</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050190.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>美媒：幕僚建議川普 打擊伊朗基礎設施為合理手段</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>2026/04/05 21:22</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2026-04-05T21:22:00+08:00</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050186.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>中國處決涉販毒法國公民 法外交部發聲譴責</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>2026/04/05 20:35</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2026-04-05T20:35:00+08:00</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050181.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>美軍營救困伊朗飛官 澳洲退役少將：其他國家難辦到</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>2026/04/05 18:43</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2026-04-05T18:43:00+08:00</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050168.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>伊朗全國斷網37天 創全球最久紀錄</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2026/04/05 18:14</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2026-04-05T18:14:00+08:00</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050162.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>伊朗攻擊中東多國 科威特、巴林、阿聯設施遇襲</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>2026/04/05 16:58</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2026-04-05T16:58:00+08:00</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050132.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>4月5日 美伊戰爭對國際經濟、財經市場與民生衝擊</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2026/04/05 16:50</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>2026-04-05T16:50:00+08:00</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050128.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>伊朗局部解封荷莫茲海峽 允許基本物資船隻通行</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2026/04/05 16:50</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>2026-04-05T16:50:00+08:00</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050127.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>美國營救受困伊朗飛官細節曝光 犧牲兩架MC-130J特戰運輸機</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>2026/04/05 16:16</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2026-04-05T16:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050117.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>烏克蘭無人機襲擊 俄國波羅的海港口輸油管線受損</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2026/04/05 14:47</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2026-04-05T14:47:00+08:00</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050096.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>從緬甸軍政府領袖到總統 敏昂萊奪權5年後登上大位</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2026/04/05 14:32</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2026-04-05T14:32:00+08:00</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050089.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>伊朗戰爭擾航運 韓國要求波灣國家維持能源供應穩定</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2026/04/05 14:30</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2026-04-05T14:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050086.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Anthropic傳遭美列國安黑名單 英國力邀投資布局</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2026/04/05 14:20</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2026-04-05T14:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050083.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>德國國防新制 役男出國超過3個月須軍方批准</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2026/04/05 14:17</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2026-04-05T14:17:00+08:00</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050081.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>中東戰爭衝擊供應鏈 藥品物流需求激增</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2026/04/05 13:25</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2026-04-05T13:25:00+08:00</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050073.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>傳美長程飛彈盡出對付伊朗 若其他強敵出現恐缺彈藥</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2026/04/05 12:44</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2026-04-05T12:44:00+08:00</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604053002.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>川普宣布美軍飛行員獲救 困伊朗逾24小時突襲脫險</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2026/04/05 12:34</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2026-04-05T12:34:00+08:00</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050064.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>應美政府要求 衛星公司無限期停止發布中東影像</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2026/04/05 12:17</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2026-04-05T12:17:00+08:00</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050062.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>中東局勢升溫衝擊旅遊 亞洲旅客轉向東南亞航線</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2026/04/05 11:37</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2026-04-05T11:37:00+08:00</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050043.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>中東戰爭第36天》川普放話、伊朗反批威脅愚蠢 最新發展一次看</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2026/04/05 11:37</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>2026-04-05T11:37:00+08:00</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050041.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>中東戰爭致油價飆漲 歐盟5國主張課徵能源暴利稅</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2026/04/05 10:45</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2026-04-05T10:45:00+08:00</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050031.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>不滿蓋茲與艾普斯坦往來 巴菲特擬停捐蓋茲基金會</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2026/04/05 10:34</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>2026-04-05T10:34:00+08:00</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050028.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>教宗主持復活節守夜彌撒 籲世人切勿對戰爭麻木</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2026/04/05 09:44</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>2026-04-05T09:44:00+08:00</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050020.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>川普伊朗互嗆「地獄」 美以施壓德黑蘭開放海峽</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2026/04/05 09:03</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>2026-04-05T09:03:00+08:00</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050015.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>以色列街頭反戰抗議不斷 尼坦雅胡：繼續打伊朗</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2026/04/05 08:39</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2026-04-05T08:39:00+08:00</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050012.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>復活節義大利「巧克力蛋」成山 從足球到精品都有驚喜</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2026/04/05 08:33</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>2026-04-05T08:33:00+08:00</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604053001.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>美路易斯安那州寮國新年活動傳車禍 至少15傷</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>2026/04/05 08:14</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>2026-04-05T08:14:00+08:00</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050010.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>川普稱大規模攻擊德黑蘭 多名伊朗軍方領導人喪命[影]</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2026/04/05 06:30</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>2026-04-05T06:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/aopl/202604050009.aspx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
